--- a/data/trans_orig/IP25B02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68334</t>
+          <t>67257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44052</t>
+          <t>42010</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87379</t>
+          <t>90833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>36680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>36718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>43624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67375</t>
+          <t>67536</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,63%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24698</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39852</t>
+          <t>40286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46661</t>
+          <t>47490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54965</t>
+          <t>54454</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80699</t>
+          <t>81602</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46630</t>
+          <t>46128</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>24006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>44621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58688</t>
+          <t>58133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83902</t>
+          <t>87393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30176</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29903</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>59644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48616</t>
+          <t>48766</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81544</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39004</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>59323</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>57439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84349</t>
+          <t>83574</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100814</t>
+          <t>101801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136711</t>
+          <t>135365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61623</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61881</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88175</t>
+          <t>88044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108767</t>
+          <t>109262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143754</t>
+          <t>144672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58317</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84138</t>
+          <t>84703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54558</t>
+          <t>55632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79235</t>
+          <t>81354</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118627</t>
+          <t>117925</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158094</t>
+          <t>156872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35943</t>
+          <t>35806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109418</t>
+          <t>109047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>29795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>54861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75080</t>
+          <t>73348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169202</t>
+          <t>162862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>55829</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42667</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>66359</t>
+          <t>65824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69350</t>
+          <t>72710</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112457</t>
+          <t>113686</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28589</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61881</t>
+          <t>60577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40520</t>
+          <t>40295</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66177</t>
+          <t>67053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76549</t>
+          <t>73390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120178</t>
+          <t>119034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>23999</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48910</t>
+          <t>49809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>44247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>53847</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86450</t>
+          <t>87428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>25591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18720</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>35415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34314</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56120</t>
+          <t>57747</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36610</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57585</t>
+          <t>56559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38830</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61430</t>
+          <t>60548</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81367</t>
+          <t>80132</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109552</t>
+          <t>110292</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37162</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56513</t>
+          <t>57525</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44142</t>
+          <t>43614</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65717</t>
+          <t>65239</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87057</t>
+          <t>86859</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>116685</t>
+          <t>116900</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>40480</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61561</t>
+          <t>61551</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41016</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60765</t>
+          <t>61843</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88355</t>
+          <t>86796</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117027</t>
+          <t>115877</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85106</t>
+          <t>86264</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>187396</t>
+          <t>218937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>126639</t>
+          <t>124530</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>185511</t>
+          <t>188601</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>225799</t>
+          <t>228551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>341460</t>
+          <t>359144</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>139243</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>189588</t>
+          <t>186463</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>174359</t>
+          <t>175655</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>223244</t>
+          <t>221746</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>331008</t>
+          <t>328278</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>395008</t>
+          <t>398350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>150845</t>
+          <t>150418</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>198535</t>
+          <t>198701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>193036</t>
+          <t>194750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>241405</t>
+          <t>242104</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,47 +3282,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>32,15%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>393865</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>359621</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>426414</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>25,64%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>393865</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>357658</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>430058</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>28,08%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>25,5%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>167760</t>
+          <t>169819</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>219397</t>
+          <t>218479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>162605</t>
+          <t>165842</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>204902</t>
+          <t>207439</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>345622</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>414485</t>
+          <t>411655</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25B02_2023-Habitat-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos en fines de semana / solo 2023 en 2023 (tasa de respuesta: 98,12%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos en fin de semana en 2023 (tasa de respuesta: 98,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34412</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23795</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>54057</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>18,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15005</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9402</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22091</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43412</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30463</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67257</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>58417</t>
+          <t>50417</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42010</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90833</t>
+          <t>71855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26068</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17355</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35529</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>28547</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21554</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36680</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25,08%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>18,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,23%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>30932</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18132</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36718</t>
+          <t>39488</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54566</t>
+          <t>57000</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43624</t>
+          <t>46039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67536</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26806</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>46095</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>21,39%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>36,78%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>32117</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25183</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>40286</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28,22%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,4%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>36532</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25643</t>
+          <t>26086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47490</t>
+          <t>43716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>68648</t>
+          <t>70297</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>54454</t>
+          <t>56716</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81602</t>
+          <t>83383</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28606</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20761</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37792</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>22,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>38138</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30323</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46128</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>36589</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24006</t>
+          <t>29673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44621</t>
+          <t>45374</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71996</t>
+          <t>65194</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58133</t>
+          <t>54061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87393</t>
+          <t>77031</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>125322</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>125322</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>125322</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>113806</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>113806</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>113806</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>139822</t>
+          <t>117586</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>139822</t>
+          <t>117586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>139822</t>
+          <t>117586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>253627</t>
+          <t>242908</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>253627</t>
+          <t>242908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253627</t>
+          <t>242908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39194</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28936</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>55656</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>20730</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>13738</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>29087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>15,36%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>41416</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30750</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59644</t>
+          <t>29298</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>62146</t>
+          <t>60121</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>48043</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>80973</t>
+          <t>78730</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>66624</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>55438</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>79903</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>28,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>23,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>48672</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38627</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59323</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>69634</t>
+          <t>50091</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57439</t>
+          <t>41329</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83574</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>118305</t>
+          <t>116715</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101801</t>
+          <t>102133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135365</t>
+          <t>133426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72347</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60046</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86170</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>30,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50882</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39989</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>61017</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>32,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74154</t>
+          <t>51875</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61043</t>
+          <t>41313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88044</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>125036</t>
+          <t>124223</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109262</t>
+          <t>106921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144672</t>
+          <t>140099</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56587</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46599</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69134</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24,1%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>69050</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58229</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>84703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,75%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,74%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67231</t>
+          <t>60485</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>50414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81354</t>
+          <t>70954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>136282</t>
+          <t>117072</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117925</t>
+          <t>102186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>156872</t>
+          <t>133795</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>234752</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>189334</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>189334</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>189334</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>183377</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>183377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252435</t>
+          <t>183377</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>441769</t>
+          <t>418130</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441769</t>
+          <t>418130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>441769</t>
+          <t>418130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40232</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29755</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>53314</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>18,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,56%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>59946</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>35806</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>109047</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>32,55%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>36781</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29795</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54861</t>
+          <t>48448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>100855</t>
+          <t>77013</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>73348</t>
+          <t>62233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162862</t>
+          <t>91915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49728</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39598</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>61090</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30,37%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>40826</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>25355</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>55829</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>22,17%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>30,32%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53457</t>
+          <t>36816</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>28012</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65824</t>
+          <t>47082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>94283</t>
+          <t>86544</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>72710</t>
+          <t>71909</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>113686</t>
+          <t>102053</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46117</t>
+          <t>46333</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28444</t>
+          <t>36595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60577</t>
+          <t>60914</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>52650</t>
+          <t>40996</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40295</t>
+          <t>32419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67053</t>
+          <t>50980</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>98767</t>
+          <t>87329</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73390</t>
+          <t>73709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119034</t>
+          <t>103024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27472</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20043</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35535</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,78%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>37257</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23999</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>49809</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>20,23%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>27,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33662</t>
+          <t>36516</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25086</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44247</t>
+          <t>46199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>70920</t>
+          <t>63988</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53847</t>
+          <t>53068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87428</t>
+          <t>76859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>163765</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>163765</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>163765</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>184147</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>184147</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>184147</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>151109</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>314874</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>314874</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>314874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>24491</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17688</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>33760</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>14,56%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20,06%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>18333</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>12030</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>25591</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25892</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>43242</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>33952</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57747</t>
+          <t>56394</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>45376</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>35039</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>55315</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>26,97%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>20,82%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>32,87%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>46366</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>36796</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>56559</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>22,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>48836</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60548</t>
+          <t>57698</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>95202</t>
+          <t>93009</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80132</t>
+          <t>79898</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110292</t>
+          <t>109231</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>50347</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>41719</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>61258</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>29,92%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>36,41%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>47134</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>38676</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>57525</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>29,07%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>23,85%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>54280</t>
+          <t>48674</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>39245</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65239</t>
+          <t>58852</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>101413</t>
+          <t>99022</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>86859</t>
+          <t>84121</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>116900</t>
+          <t>112887</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>48047</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>38158</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>58590</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>28,56%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>22,68%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>34,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>50311</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>40480</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>61551</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>31,03%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51067</t>
+          <t>46525</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41476</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61843</t>
+          <t>55393</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>101378</t>
+          <t>94572</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86796</t>
+          <t>81702</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115877</t>
+          <t>108818</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>168261</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>168261</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>168261</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>162144</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>162144</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>162144</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>161583</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>161583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>180075</t>
+          <t>161583</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>329844</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>329844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>329844</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2996,72 +2996,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>138329</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>116632</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>167913</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>114015</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>86264</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>218937</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>13,28%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>151628</t>
+          <t>92464</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>124530</t>
+          <t>77079</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>188601</t>
+          <t>109104</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>265643</t>
+          <t>230793</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>228551</t>
+          <t>204123</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>359144</t>
+          <t>264423</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -3109,72 +3109,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>187796</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>166155</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>210546</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>27,13%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>30,42%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>164409</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>139243</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>186463</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>28,71%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>197947</t>
+          <t>165472</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>175655</t>
+          <t>147236</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>221746</t>
+          <t>185905</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>362356</t>
+          <t>353268</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>325779</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398350</t>
+          <t>382807</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -3222,72 +3222,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>205265</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>183932</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>230498</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>29,66%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>176249</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>150418</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>198701</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>27,14%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>30,6%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>217616</t>
+          <t>175606</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>194750</t>
+          <t>158952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>242104</t>
+          <t>195763</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>393865</t>
+          <t>380870</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359621</t>
+          <t>353107</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>426414</t>
+          <t>412017</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -3335,72 +3335,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>160712</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>143086</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>179366</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>23,22%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>25,92%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>194756</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>169819</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>218479</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>33,64%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>185818</t>
+          <t>180114</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>165842</t>
+          <t>163510</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>207439</t>
+          <t>200514</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>380574</t>
+          <t>340826</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>314655</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>411655</t>
+          <t>369055</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -3448,57 +3448,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>692101</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>649430</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>753009</t>
+          <t>613656</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1402439</t>
+          <t>1305757</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
